--- a/sports_forms/023_softball_player_finder_form_template--sports_forms.xlsx
+++ b/sports_forms/023_softball_player_finder_form_template--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'9-12'}</t>
+          <t>9-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '9-12'}</t>
+          <t>9-12</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'13-15'}</t>
+          <t>13-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '13-15'}</t>
+          <t>13-15</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'16-18'}</t>
+          <t>16-18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '16-18'}</t>
+          <t>16-18</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pitcher'}</t>
+          <t>pitcher</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pitcher'}</t>
+          <t>Pitcher</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'catcher'}</t>
+          <t>catcher</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Catcher'}</t>
+          <t>Catcher</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'infielder'}</t>
+          <t>infielder</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Infielder'}</t>
+          <t>Infielder</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'outfielder'}</t>
+          <t>outfielder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Outfielder'}</t>
+          <t>Outfielder</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'local_team'}</t>
+          <t>local_team</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Local Team'}</t>
+          <t>Local Team</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'regional_team'}</t>
+          <t>regional_team</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Regional Team'}</t>
+          <t>Regional Team</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'national_team'}</t>
+          <t>national_team</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'National Team'}</t>
+          <t>National Team</t>
         </is>
       </c>
     </row>
